--- a/results/Int All Data -0.5/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_2_permute.xlsx
@@ -440,1137 +440,1137 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8950401427297057</v>
+        <v>0.865563801317213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8950991705733862</v>
+        <v>0.8495676352800501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8962341754132899</v>
+        <v>0.8472976256002429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8956742649989561</v>
+        <v>0.8472976256002429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8970453812135821</v>
+        <v>0.8468996147057148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8964854707992485</v>
+        <v>0.85112931083569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8941125894433162</v>
+        <v>0.8511444948469262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8891307153567294</v>
+        <v>0.8514986619090099</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8891307153567294</v>
+        <v>0.852986125609733</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8780033025224439</v>
+        <v>0.8463734887163816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8848116233606014</v>
+        <v>0.8515897659764269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.883809858219295</v>
+        <v>0.8515897659764269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8840307855827814</v>
+        <v>0.8500584584432593</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8750570349422058</v>
+        <v>0.8463734887163816</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8760301402623039</v>
+        <v>0.8432636134150739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8760301402623039</v>
+        <v>0.8327247708163303</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8762072237933456</v>
+        <v>0.8299825383870784</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8882470059027844</v>
+        <v>0.841022263556475</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8864930628048665</v>
+        <v>0.8410812914001556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8885859889536318</v>
+        <v>0.8424658834247538</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8891020555355211</v>
+        <v>0.8410661073889194</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8908408146222029</v>
+        <v>0.8431876933588931</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8899419211570216</v>
+        <v>0.8511462030481902</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8900009490007023</v>
+        <v>0.8418907889991838</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8900009490007023</v>
+        <v>0.8380152599312923</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8892791390665629</v>
+        <v>0.8337248277563725</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8897496536147437</v>
+        <v>0.8335039003928864</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8842668969575037</v>
+        <v>0.8355529827092072</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8849887068916431</v>
+        <v>0.829938694554634</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8834556911572115</v>
+        <v>0.8312355989143432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8843259248011843</v>
+        <v>0.8200036062026685</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8843259248011843</v>
+        <v>0.8001064778787936</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8812160494998766</v>
+        <v>0.8038201074268795</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.87978590544157</v>
+        <v>0.8124127393854272</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8737584223812325</v>
+        <v>0.8048218725681857</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8588600603564447</v>
+        <v>0.8012111146962249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8590219598762503</v>
+        <v>0.8024793592347258</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8590219598762503</v>
+        <v>0.8013595384060583</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8647846717406571</v>
+        <v>0.7893045722853835</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8640476777952815</v>
+        <v>0.789363600129064</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8587015772391671</v>
+        <v>0.7858557139332283</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8445519767684628</v>
+        <v>0.7874916013437849</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8491796837929659</v>
+        <v>0.7859147417769089</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8402632527948071</v>
+        <v>0.7872706739802987</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8459821208267694</v>
+        <v>0.7871660941029097</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.846924858124395</v>
+        <v>0.787107066259229</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8378465276064304</v>
+        <v>0.7745191413441646</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8404420445271129</v>
+        <v>0.7745191413441646</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8355343822954429</v>
+        <v>0.7476804524835348</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8334414561466776</v>
+        <v>0.7460884089054225</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8341194222483725</v>
+        <v>0.7447324767020327</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7789359804126255</v>
+        <v>0.7495220832463416</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7765630990566933</v>
+        <v>0.7360538652798603</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7890701691119251</v>
+        <v>0.7385161425019455</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8116505020213716</v>
+        <v>0.7446937574733805</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7626260747432954</v>
+        <v>0.7416260178032532</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7633934367111431</v>
+        <v>0.7416260178032532</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7515863495738987</v>
+        <v>0.7416260178032532</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7515863495738987</v>
+        <v>0.7322660238768577</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7515863495738987</v>
+        <v>0.7342847381707063</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7329692333972326</v>
+        <v>0.7424338072010174</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7382310626909864</v>
+        <v>0.7352274754683319</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7018215119479189</v>
+        <v>0.7335342684153586</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7045485603659347</v>
+        <v>0.7335342684153586</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7052265264676296</v>
+        <v>0.7487463700723138</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7162358836145539</v>
+        <v>0.7445318579535749</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7066701463359083</v>
+        <v>0.7523874959667469</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.704577220187143</v>
+        <v>0.7523874959667469</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.698993300055042</v>
+        <v>0.7586055383680983</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7034152637272951</v>
+        <v>0.7591654487824321</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7035063677947122</v>
+        <v>0.755141496004707</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6901696813255642</v>
+        <v>0.7326758023800938</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6844221534723935</v>
+        <v>0.7351380796021789</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6953168713344848</v>
+        <v>0.7342982139806784</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.695139787803443</v>
+        <v>0.7528107502799553</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6823563687437129</v>
+        <v>0.7379089718526392</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6823563687437129</v>
+        <v>0.7379089718526392</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6944872549205686</v>
+        <v>0.7479604076907017</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6791284377550439</v>
+        <v>0.7457663180670753</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6936287888853038</v>
+        <v>0.7457663180670753</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6930098506272895</v>
+        <v>0.7401520299125022</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6857141230284511</v>
+        <v>0.7364535843756524</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6886738664186611</v>
+        <v>0.7276956364947711</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6898544232922732</v>
+        <v>0.6784620494619167</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6673129994116196</v>
+        <v>0.6803930760908763</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.626247271622981</v>
+        <v>0.6804521039345569</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6300654810484559</v>
+        <v>0.6749103194336363</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6408926300605462</v>
+        <v>0.6715660409588703</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6257177292311196</v>
+        <v>0.6724632262227874</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6208622620380739</v>
+        <v>0.6701932165429803</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6513251845806366</v>
+        <v>0.6375749236054434</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6340539411999164</v>
+        <v>0.6032903752348777</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6336407462941522</v>
+        <v>0.603909313492892</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6058610283371609</v>
+        <v>0.6008584660352648</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5854341678212842</v>
+        <v>0.6000624442462088</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5876451496574107</v>
+        <v>0.5795160096418471</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5902541423880654</v>
+        <v>0.5750805701596219</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5807373735456565</v>
+        <v>0.5741664926832046</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5753440127545695</v>
+        <v>0.5925019454514396</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5715426955415946</v>
+        <v>0.5982208134834019</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5699506519634825</v>
+        <v>0.6113686488128002</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.576681344544195</v>
+        <v>0.6075369635773531</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.576681344544195</v>
+        <v>0.6078759466282005</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5848826086131304</v>
+        <v>0.6094528061950766</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5833074572475183</v>
+        <v>0.5350484939358855</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5543589500256231</v>
+        <v>0.5333097348492037</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5446127128134075</v>
+        <v>0.5477679503482833</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5126672613737734</v>
+        <v>0.5222851936910433</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5127549490386623</v>
+        <v>0.5226241767418908</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5128578207147874</v>
+        <v>0.5226241767418908</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5143166245943023</v>
+        <v>0.5220052384838765</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5076094672310058</v>
+        <v>0.5196323571279443</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5063277468825327</v>
+        <v>0.5196323571279443</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5056497807808378</v>
+        <v>0.5199713401787918</v>
       </c>
     </row>
     <row r="116">
@@ -1580,407 +1580,407 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5046328316282954</v>
+        <v>0.5196323571279443</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5017269914779737</v>
+        <v>0.5279467420805891</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5012261089073206</v>
+        <v>0.533031487843301</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.502345929735988</v>
+        <v>0.5180706815723044</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5006510144817506</v>
+        <v>0.5162577106307058</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.498719987852791</v>
+        <v>0.5096247651223262</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5014605120807789</v>
+        <v>0.5128526961109952</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5011501888511397</v>
+        <v>0.5029631597927382</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5011501888511397</v>
+        <v>0.499897128323875</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5011501888511397</v>
+        <v>0.5041723764875586</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5025061210545296</v>
+        <v>0.5034792263746275</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5020490823163209</v>
+        <v>0.5043781198398087</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5022109818361266</v>
+        <v>0.5026832045855714</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5024909370432934</v>
+        <v>0.4966422457152618</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5024909370432934</v>
+        <v>0.4965832178715812</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5018129709415985</v>
+        <v>0.49646516218422</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5011940326835842</v>
+        <v>0.4625636304970865</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.501473987890751</v>
+        <v>0.4625636304970865</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.501473987890751</v>
+        <v>0.4630206692352953</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5010169491525424</v>
+        <v>0.4503501812591341</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5013559322033898</v>
+        <v>0.4472116461366182</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5020338983050847</v>
+        <v>0.4483314669652856</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5020338983050847</v>
+        <v>0.4486114221724524</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5017539430979179</v>
+        <v>0.4892149866190901</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5017539430979179</v>
+        <v>0.4911898570804942</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5017539430979179</v>
+        <v>0.4909099018733274</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5017539430979179</v>
+        <v>0.4907480023535217</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5017539430979179</v>
+        <v>0.4857088086245184</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5015330157344317</v>
+        <v>0.4988801791713326</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5011940326835842</v>
+        <v>0.4988801791713326</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5003980108945281</v>
+        <v>0.4986002239641658</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5007960217890561</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5007960217890561</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5007960217890561</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5002361113747225</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000590278436806</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5000590278436806</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5014149600470704</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5014149600470704</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5014149600470704</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5005160665818893</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
